--- a/data/designs.xlsx
+++ b/data/designs.xlsx
@@ -5,23 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam\Desktop\EventDecor\event-decoration-site\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0513E5-12B5-4A3A-B269-CC445B6640CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED2DB25-7E51-4921-9610-88378457E8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Designs" sheetId="1" r:id="rId1"/>
-    <sheet name="Notes" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -50,78 +49,15 @@
     <t>type</t>
   </si>
   <si>
-    <t>Princess Pink Theme</t>
-  </si>
-  <si>
-    <t>https://objectstorage.example.com/designs/princess.jpg</t>
-  </si>
-  <si>
-    <t>Beautiful princess birthday decoration setup</t>
-  </si>
-  <si>
-    <t>5 years</t>
-  </si>
-  <si>
-    <t>female</t>
-  </si>
-  <si>
-    <t>princess</t>
-  </si>
-  <si>
     <t>birthday</t>
   </si>
   <si>
-    <t>Superhero Party</t>
-  </si>
-  <si>
-    <t>https://objectstorage.example.com/designs/superhero.jpg</t>
-  </si>
-  <si>
-    <t>Marvel superhero birthday setup</t>
-  </si>
-  <si>
-    <t>7 years</t>
-  </si>
-  <si>
     <t>male</t>
   </si>
   <si>
-    <t>superhero</t>
-  </si>
-  <si>
-    <t>Jungle Safari Theme</t>
-  </si>
-  <si>
-    <t>https://objectstorage.example.com/designs/jungle.jpg</t>
-  </si>
-  <si>
-    <t>Jungle safari balloon decoration</t>
-  </si>
-  <si>
-    <t>4 years</t>
-  </si>
-  <si>
     <t>all</t>
   </si>
   <si>
-    <t>jungle</t>
-  </si>
-  <si>
-    <t>Unicorn Fantasy</t>
-  </si>
-  <si>
-    <t>https://objectstorage.example.com/designs/unicorn.jpg</t>
-  </si>
-  <si>
-    <t>Magical unicorn birthday theme</t>
-  </si>
-  <si>
-    <t>6 years</t>
-  </si>
-  <si>
-    <t>unicorn</t>
-  </si>
-  <si>
     <t>Boss Baby Setup</t>
   </si>
   <si>
@@ -134,52 +70,79 @@
     <t>boss baby</t>
   </si>
   <si>
-    <t>Romantic Anniversary</t>
-  </si>
-  <si>
-    <t>https://objectstorage.example.com/designs/anniversary.jpg</t>
-  </si>
-  <si>
-    <t>Romantic anniversary room decoration</t>
-  </si>
-  <si>
-    <t>romantic</t>
-  </si>
-  <si>
-    <t>anniversary</t>
-  </si>
-  <si>
-    <t>Frozen Blue Theme</t>
-  </si>
-  <si>
-    <t>https://objectstorage.example.com/designs/frozen.jpg</t>
-  </si>
-  <si>
-    <t>Elegant frozen-inspired birthday decor</t>
-  </si>
-  <si>
-    <t>8 years</t>
-  </si>
-  <si>
-    <t>frozen</t>
-  </si>
-  <si>
-    <t>Elegant Rose Anniversary</t>
-  </si>
-  <si>
-    <t>https://objectstorage.example.com/designs/rose-anniversary.jpg</t>
-  </si>
-  <si>
-    <t>Premium romantic anniversary decoration</t>
-  </si>
-  <si>
-    <t>rose</t>
-  </si>
-  <si>
-    <t>Image column expects object storage endpoint URL. Replace the sample URLs with your real CDN/object storage links.</t>
-  </si>
-  <si>
     <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/JaZ4VVLq8rPAZFGUnrXvYlPQQa3GPmYfU3ujEBRNK1Ab1AVjrOazTA2HTjURDEWj/n/bmd455xcti4w/b/Birthday/o/1_2ChicDecor1_2ChicDecor.png</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/o3U4nMAOUoqCBkDpdk6Gt-eNUDEGjPJKnaHedPWcAQE-lyUIVJxK7XN7t183wBqR/n/bmd455xcti4w/b/Birthday/o/1_1paw_patrol1_1paw_patrol.jpg</t>
+  </si>
+  <si>
+    <t>Paw Patrol</t>
+  </si>
+  <si>
+    <t>Paw Patrol Celebration</t>
+  </si>
+  <si>
+    <t>paw patrol</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>cartoon</t>
+  </si>
+  <si>
+    <t>peppa pig</t>
+  </si>
+  <si>
+    <t>Peppa Pig</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/6r9lXvdNXunfknxXDcKzqDhJt-coquiqab8mVPgw3v0FkpjF7xCJ2YFpAHq4Xpt-/n/bmd455xcti4w/b/Birthday/o/1_8_Peppa_pig_Cartoon1_8_Peppa_pig_Cartoon.jpg</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/K9GsjHA3dpG1S6c6m0YmXXpolApFFomObTbMrlF_TQ7c4lgExCdXwIoK0n9CE0jM/n/bmd455xcti4w/b/Birthday/o/1_Cocomelon1_Cocomelon.jpg</t>
+  </si>
+  <si>
+    <t>Cocomelon</t>
+  </si>
+  <si>
+    <t>disney</t>
+  </si>
+  <si>
+    <t>cocomelon</t>
+  </si>
+  <si>
+    <t>mickey mouse</t>
+  </si>
+  <si>
+    <t>Mickey Mouse</t>
+  </si>
+  <si>
+    <t>1-5 years</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/aNVKj7buN0ybClp1083cIjXeJRDVEariEs2l69Wvxva3C1DUAnWaVu1oAcdWNODn/n/bmd455xcti4w/b/Birthday/o/1_7_mickey_mouse1_7_mickey_mouse.jpg</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/nJbOZq7FQe-R7WYiN7ByOio2Doy6eZSz-TCVsw39DWOC0GWNIQYDQ8qdjLgabGYr/n/bmd455xcti4w/b/Birthday/o/Silver_Pink_BlissSilver_Pink_Decor.jpg</t>
+  </si>
+  <si>
+    <t>silver and pink décor</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>Infant(0–1 year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bubble Trouble Balloon </t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/qDSlCXIrg1qdPEURLaLB9WXCWxapsyYHR_TAYy-RmYaP-CvwO4qMyVDzcJue6CBg/n/bmd455xcti4w/b/Birthday/o/InfantInfant_Bubble_Trouble_Balloon%20.jpg</t>
   </si>
 </sst>
 </file>
@@ -189,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\₹#,##0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -198,6 +161,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -223,10 +192,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -237,8 +207,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -403,20 +380,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="3" max="3" width="48" style="4" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="6" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" customHeight="1">
+    <row r="1" spans="1:10" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,267 +416,238 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1">
+    <row r="2" spans="1:10" ht="24" customHeight="1">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5499</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3">
-        <v>4999</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="24" customHeight="1">
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="70">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="3">
-        <v>5999</v>
+        <v>2500</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="24" customHeight="1">
+      <c r="J3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="70">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>6999</v>
+        <v>2500</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="56">
+      <c r="A5" s="2">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="D5" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="24" customHeight="1">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="70">
+      <c r="A6" s="2">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3">
-        <v>7999</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="J6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="70">
+      <c r="A7" s="2">
         <v>13</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="24" customHeight="1">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5499</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="D7" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="24" customHeight="1">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="70">
+      <c r="A8" s="2">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="3">
-        <v>9999</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="24" customHeight="1">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6499</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="24" customHeight="1">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="3">
-        <v>10999</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="90" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="26.65" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{2ED8239C-41F5-4902-85A7-527479D51239}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>

--- a/data/designs.xlsx
+++ b/data/designs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam\Desktop\EventDecor\event-decoration-site\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED2DB25-7E51-4921-9610-88378457E8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368741E0-D245-4D83-82FE-B42F819F8F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -52,12 +52,6 @@
     <t>birthday</t>
   </si>
   <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
     <t>Boss Baby Setup</t>
   </si>
   <si>
@@ -70,9 +64,6 @@
     <t>boss baby</t>
   </si>
   <si>
-    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/JaZ4VVLq8rPAZFGUnrXvYlPQQa3GPmYfU3ujEBRNK1Ab1AVjrOazTA2HTjURDEWj/n/bmd455xcti4w/b/Birthday/o/1_2ChicDecor1_2ChicDecor.png</t>
-  </si>
-  <si>
     <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/o3U4nMAOUoqCBkDpdk6Gt-eNUDEGjPJKnaHedPWcAQE-lyUIVJxK7XN7t183wBqR/n/bmd455xcti4w/b/Birthday/o/1_1paw_patrol1_1paw_patrol.jpg</t>
   </si>
   <si>
@@ -143,6 +134,12 @@
   </si>
   <si>
     <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/qDSlCXIrg1qdPEURLaLB9WXCWxapsyYHR_TAYy-RmYaP-CvwO4qMyVDzcJue6CBg/n/bmd455xcti4w/b/Birthday/o/InfantInfant_Bubble_Trouble_Balloon%20.jpg</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/A8OflrQe9KbmKkAt4BTqkKDn83Z6BvCyt93SL2cMBy3SeWm_N3Xcay3Ts-cGfFN-/n/bmd455xcti4w/b/Birthday/o/Infantboss_baby.jpg</t>
+  </si>
+  <si>
+    <t>All</t>
   </si>
 </sst>
 </file>
@@ -416,7 +413,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -430,26 +427,26 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D2" s="3">
-        <v>5499</v>
+        <v>2700</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>9</v>
@@ -460,28 +457,28 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3">
         <v>2500</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>9</v>
@@ -492,28 +489,28 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3">
         <v>2500</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>9</v>
@@ -524,25 +521,28 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3">
         <v>2500</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>9</v>
@@ -553,28 +553,28 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3">
         <v>2500</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>9</v>
@@ -585,28 +585,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7" s="3">
         <v>2600</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>9</v>
@@ -617,28 +617,28 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D8" s="3">
         <v>1700</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>

--- a/data/designs.xlsx
+++ b/data/designs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam\Desktop\EventDecor\event-decoration-site\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368741E0-D245-4D83-82FE-B42F819F8F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44EF51F-26BB-4DB2-BF95-202355603E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -140,6 +140,39 @@
   </si>
   <si>
     <t>All</t>
+  </si>
+  <si>
+    <t>anniversary</t>
+  </si>
+  <si>
+    <t>Metallic Balloons  Style</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/T-09sosMD-1FeeqU41d71qA_lqxHzGRPq-fA5eT_Kw26qGPHkBbun82lpMhyqOd2/n/bmd455xcti4w/b/Anniversary/o/AnniversaryAnniversary_mettalic_Balloon.jpg</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/wQNzvOozW_3exnzcu_zvac8pii-_SuzqH0HgiooYj6HeGAo22bPr_vkA3SlCh6Rp/n/bmd455xcti4w/b/Anniversary/o/Anniversary1_1white_blue_stage.png</t>
+  </si>
+  <si>
+    <t>White Blue Stage</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/uocc4qZu-mR5m0m7EneG_ajQqn3fgE0GFdP3iU0KnXN3dTnytv_s6d7bJtu1pWAc/n/bmd455xcti4w/b/Anniversary/o/anniversary1_3Rosegold.png</t>
+  </si>
+  <si>
+    <t>Rose Gold Style</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/5aRnzShpWmLDNj8IBfOa6n3fRmgatYiMBl82ndLA6CXPIAuq78aniqB9ovmBkIKd/n/bmd455xcti4w/b/Anniversary/o/Anniversary1_2Third_Anniversary.png</t>
+  </si>
+  <si>
+    <t>Black And White Style</t>
+  </si>
+  <si>
+    <t>https://objectstorage.ap-mumbai-1.oraclecloud.com/p/gF97j8xvamQr8Sg7DvHBRkJTi-G21n32eEDib2Q_z563B4UV-s7ZMvrQ5jTLpyMj/n/bmd455xcti4w/b/Anniversary/o/AnniversaryBlue_Ring_anniversary.jpeg</t>
+  </si>
+  <si>
+    <t>Blue Ring Style</t>
   </si>
 </sst>
 </file>
@@ -377,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -642,6 +675,109 @@
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="70">
+      <c r="A10" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="70">
+      <c r="A11" s="2">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="56">
+      <c r="A12" s="2">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="70">
+      <c r="A13" s="2">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
